--- a/docs/Capitolis_CCR_Parametric_Benchmarks.xlsx
+++ b/docs/Capitolis_CCR_Parametric_Benchmarks.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity &amp; FX vol" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rate vol" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation cross-check" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity vega bump" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -77934,4 +77935,326 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>4. Bumping equity volatility: closed-form vega vs Monte Carlo vega</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>A hypothetical $1,000,000 receive-equity position, struck at today's spot (K=S0). Its expected exposure at a future date T is E[max(S_T-K,0)] per share, which for a lognormal S_T has the closed-form (undiscounted Black) formula below -- live in this sheet -- bumped +/-1% relative vol, and checked against the same bump run through the Monte Carlo engine (N=5,000, Latin Hypercube, same seed as the base run).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Spot S0</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>182.3000030517578</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Strike K (= S0, ATM)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>182.3000030517578</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Base volatility</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7603962743766229</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Notional (USD)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Shares (= notional / S0)</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>C7/C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Node T (years, ~1y)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Deterministic r (zero rate to T, from today's curve)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.04055569407986093</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dividend yield q</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>F = S0*EXP((r-q)*T)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>d1</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>d2</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Closed-form E[max(S_T-K,0)] per share (undiscounted Black)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>x Shares = USD EE (closed-form)</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Simulated USD EE (Monte Carlo, same node)</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.7603962743766229</v>
+      </c>
+      <c r="C15">
+        <f>$C$4*EXP(($C$11-$C$12)*$C$10)</f>
+        <v/>
+      </c>
+      <c r="D15">
+        <f>(LN(C15/$C$5)+0.5*B15^2*$C$10)/(B15*SQRT($C$10))</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>D15-B15*SQRT($C$10)</f>
+        <v/>
+      </c>
+      <c r="F15">
+        <f>C15*NORM.S.DIST(D15,TRUE)-$C$5*NORM.S.DIST(E15,TRUE)</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>F15*$C$8</f>
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v>332323.7726488323</v>
+      </c>
+      <c r="I15">
+        <f>ABS(G15-H15)/H15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vol +1%</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.7680002371203892</v>
+      </c>
+      <c r="C16">
+        <f>$C$4*EXP(($C$11-$C$12)*$C$10)</f>
+        <v/>
+      </c>
+      <c r="D16">
+        <f>(LN(C16/$C$5)+0.5*B16^2*$C$10)/(B16*SQRT($C$10))</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>D16-B16*SQRT($C$10)</f>
+        <v/>
+      </c>
+      <c r="F16">
+        <f>C16*NORM.S.DIST(D16,TRUE)-$C$5*NORM.S.DIST(E16,TRUE)</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>F16*$C$8</f>
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v>335395.6277415191</v>
+      </c>
+      <c r="I16">
+        <f>ABS(G16-H16)/H16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Vol -1%</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7527923116328566</v>
+      </c>
+      <c r="C17">
+        <f>$C$4*EXP(($C$11-$C$12)*$C$10)</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>(LN(C17/$C$5)+0.5*B17^2*$C$10)/(B17*SQRT($C$10))</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>D17-B17*SQRT($C$10)</f>
+        <v/>
+      </c>
+      <c r="F17">
+        <f>C17*NORM.S.DIST(D17,TRUE)-$C$5*NORM.S.DIST(E17,TRUE)</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>F17*$C$8</f>
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v>329252.1387835955</v>
+      </c>
+      <c r="I17">
+        <f>ABS(G17-H17)/H17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Vega (per +1% relative vol), closed-form</t>
+        </is>
+      </c>
+      <c r="C19">
+        <f>(G16-G17)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Vega (per +1% relative vol), Monte Carlo</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>(H16-H17)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ratio (MC / closed-form)</t>
+        </is>
+      </c>
+      <c r="C21">
+        <f>C20/C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>A USD-listed name is used deliberately, so the drift is the simple r-q (no JPY quanto correction, Section 4). The closed-form formula still assumes a constant rate to T (today's zero rate) and no rate-equity correlation; the engine simulates a stochastic Hull-White short rate correlated with equities. That is a real, small, and separately-quantified source of difference (Section 7.9, model risk), not a bug: the two vegas are expected to be close, not identical.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>